--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ407"/>
+  <dimension ref="A1:AZ409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46215,10 +46215,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>104589323</v>
+        <v>136761840</v>
       </c>
       <c r="B373" t="n">
-        <v>5179</v>
+        <v>4777</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -46226,43 +46226,37 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr"/>
-      <c r="K373" t="inlineStr"/>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P373" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Lervassaskogen, Srm</t>
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>695842</v>
+        <v>695435</v>
       </c>
       <c r="R373" t="n">
-        <v>6551618</v>
+        <v>6551272</v>
       </c>
       <c r="S373" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T373" t="inlineStr">
         <is>
@@ -46286,22 +46280,22 @@
       </c>
       <c r="Y373" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD373" t="b">
@@ -46310,30 +46304,31 @@
       <c r="AE373" t="b">
         <v>0</v>
       </c>
+      <c r="AF373" t="inlineStr"/>
       <c r="AG373" t="b">
         <v>0</v>
       </c>
       <c r="AT373" t="inlineStr"/>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Axel Brandt</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>Axel Brandt</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104589323</t>
+          <t>https://artportalen.se/Sighting/136761840</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>104986969</v>
+        <v>104589323</v>
       </c>
       <c r="B374" t="n">
         <v>5179</v>
@@ -46362,19 +46357,25 @@
         </is>
       </c>
       <c r="I374" t="inlineStr"/>
+      <c r="K374" t="inlineStr"/>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P374" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>695722</v>
+        <v>695842</v>
       </c>
       <c r="R374" t="n">
-        <v>6551341</v>
+        <v>6551618</v>
       </c>
       <c r="S374" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T374" t="inlineStr">
         <is>
@@ -46398,12 +46399,22 @@
       </c>
       <c r="Y374" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD374" t="b">
@@ -46418,24 +46429,24 @@
       <c r="AT374" t="inlineStr"/>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Axel Brandt</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Axel Brandt</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104986969</t>
+          <t>https://artportalen.se/Sighting/104589323</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>117954454</v>
+        <v>104986969</v>
       </c>
       <c r="B375" t="n">
         <v>5179</v>
@@ -46464,24 +46475,19 @@
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
-      <c r="M375" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P375" t="inlineStr">
         <is>
-          <t>V Simonslund, Ornö, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>695763</v>
+        <v>695722</v>
       </c>
       <c r="R375" t="n">
-        <v>6551622</v>
+        <v>6551341</v>
       </c>
       <c r="S375" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T375" t="inlineStr">
         <is>
@@ -46505,22 +46511,12 @@
       </c>
       <c r="Y375" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="AB375" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AD375" t="b">
@@ -46535,27 +46531,27 @@
       <c r="AT375" t="inlineStr"/>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954454</t>
+          <t>https://artportalen.se/Sighting/104986969</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>136763388</v>
+        <v>117954454</v>
       </c>
       <c r="B376" t="n">
-        <v>5182</v>
+        <v>5179</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -46581,19 +46577,24 @@
         </is>
       </c>
       <c r="I376" t="inlineStr"/>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P376" t="inlineStr">
         <is>
-          <t>Lervassaskogen, Srm</t>
+          <t>V Simonslund, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>695439</v>
+        <v>695763</v>
       </c>
       <c r="R376" t="n">
-        <v>6551270</v>
+        <v>6551622</v>
       </c>
       <c r="S376" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T376" t="inlineStr">
         <is>
@@ -46617,22 +46618,22 @@
       </c>
       <c r="Y376" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD376" t="b">
@@ -46647,66 +46648,65 @@
       <c r="AT376" t="inlineStr"/>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>Emilia Blixt, Elis Bergman , Klas Magnusson, Kalle Skarin</t>
+          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136763388</t>
+          <t>https://artportalen.se/Sighting/117954454</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>104590376</v>
+        <v>136761839</v>
       </c>
       <c r="B377" t="n">
-        <v>5495</v>
+        <v>5182</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I377" t="inlineStr"/>
-      <c r="K377" t="inlineStr"/>
       <c r="P377" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Lervassaskogen, Srm</t>
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>695750</v>
+        <v>695437</v>
       </c>
       <c r="R377" t="n">
-        <v>6551167</v>
+        <v>6551273</v>
       </c>
       <c r="S377" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T377" t="inlineStr">
         <is>
@@ -46730,79 +46730,80 @@
       </c>
       <c r="Y377" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD377" t="b">
         <v>0</v>
       </c>
       <c r="AE377" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF377" t="inlineStr"/>
       <c r="AG377" t="b">
         <v>0</v>
       </c>
       <c r="AT377" t="inlineStr"/>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104590376</t>
+          <t>https://artportalen.se/Sighting/136761839</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>136763392</v>
+        <v>136763388</v>
       </c>
       <c r="B378" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I378" t="inlineStr"/>
@@ -46812,13 +46813,13 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>695495</v>
+        <v>695439</v>
       </c>
       <c r="R378" t="n">
-        <v>6551071</v>
+        <v>6551270</v>
       </c>
       <c r="S378" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T378" t="inlineStr">
         <is>
@@ -46847,7 +46848,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -46857,7 +46858,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD378" t="b">
@@ -46883,59 +46884,55 @@
       <c r="AY378" t="inlineStr"/>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136763392</t>
+          <t>https://artportalen.se/Sighting/136763388</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>117954423</v>
+        <v>104590376</v>
       </c>
       <c r="B379" t="n">
-        <v>4781</v>
+        <v>5495</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>102306</v>
+        <v>101410</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K379" t="inlineStr"/>
       <c r="P379" t="inlineStr">
         <is>
-          <t>V Simonslund, Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>695709</v>
+        <v>695750</v>
       </c>
       <c r="R379" t="n">
-        <v>6550887</v>
+        <v>6551167</v>
       </c>
       <c r="S379" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T379" t="inlineStr">
         <is>
@@ -46959,120 +46956,95 @@
       </c>
       <c r="Y379" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD379" t="b">
         <v>0</v>
       </c>
       <c r="AE379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG379" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ379" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK379" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL379" t="inlineStr">
-        <is>
-          <t>Äldre levande gran med grov bark.</t>
-        </is>
-      </c>
-      <c r="AO379" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre levande gran med grov bark.</t>
-        </is>
       </c>
       <c r="AT379" t="inlineStr"/>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954423</t>
+          <t>https://artportalen.se/Sighting/104590376</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>136747650</v>
+        <v>136763392</v>
       </c>
       <c r="B380" t="n">
-        <v>4783</v>
+        <v>5181</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>102306</v>
+        <v>102204</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr"/>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P380" t="inlineStr">
         <is>
-          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
+          <t>Lervassaskogen, Srm</t>
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>695478</v>
+        <v>695495</v>
       </c>
       <c r="R380" t="n">
-        <v>6551211</v>
+        <v>6551071</v>
       </c>
       <c r="S380" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T380" t="inlineStr">
         <is>
@@ -47099,9 +47071,19 @@
           <t>2026-09-20</t>
         </is>
       </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA380" t="inlineStr">
         <is>
           <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD380" t="b">
@@ -47116,65 +47098,70 @@
       <c r="AT380" t="inlineStr"/>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Emilia Blixt, Elis Bergman , Klas Magnusson, Kalle Skarin</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136747650</t>
+          <t>https://artportalen.se/Sighting/136763392</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>124287073</v>
+        <v>117954423</v>
       </c>
       <c r="B381" t="n">
-        <v>57364</v>
+        <v>4781</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>102954</v>
+        <v>102306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>Lervassaskogen, Lervassaskogen, Srm</t>
+          <t>V Simonslund, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>695698</v>
+        <v>695709</v>
       </c>
       <c r="R381" t="n">
-        <v>6551090</v>
+        <v>6550887</v>
       </c>
       <c r="S381" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T381" t="inlineStr">
         <is>
@@ -47198,27 +47185,22 @@
       </c>
       <c r="Y381" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC381" t="inlineStr">
-        <is>
-          <t>Spelflygande enkelbeckasin</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD381" t="b">
@@ -47229,31 +47211,51 @@
       </c>
       <c r="AG381" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ381" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK381" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL381" t="inlineStr">
+        <is>
+          <t>Äldre levande gran med grov bark.</t>
+        </is>
+      </c>
+      <c r="AO381" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre levande gran med grov bark.</t>
+        </is>
       </c>
       <c r="AT381" t="inlineStr"/>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124287073</t>
+          <t>https://artportalen.se/Sighting/117954423</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>104588894</v>
+        <v>136747650</v>
       </c>
       <c r="B382" t="n">
-        <v>58327</v>
+        <v>4783</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -47261,38 +47263,42 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>103015</v>
+        <v>102306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
-      <c r="K382" t="inlineStr"/>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P382" t="inlineStr">
         <is>
-          <t>O om Lervassaträsk, Ornö, Srm</t>
+          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>696042</v>
+        <v>695478</v>
       </c>
       <c r="R382" t="n">
-        <v>6551462</v>
+        <v>6551211</v>
       </c>
       <c r="S382" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T382" t="inlineStr">
         <is>
@@ -47316,22 +47322,12 @@
       </c>
       <c r="Y382" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z382" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB382" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD382" t="b">
@@ -47346,44 +47342,44 @@
       <c r="AT382" t="inlineStr"/>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104588894</t>
+          <t>https://artportalen.se/Sighting/136747650</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>117954456</v>
+        <v>124287073</v>
       </c>
       <c r="B383" t="n">
-        <v>58327</v>
+        <v>57364</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -47394,17 +47390,17 @@
       <c r="I383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
         <is>
-          <t>V Simonslund, Ornö, Srm</t>
+          <t>Lervassaskogen, Lervassaskogen, Srm</t>
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>695832</v>
+        <v>695698</v>
       </c>
       <c r="R383" t="n">
-        <v>6551662</v>
+        <v>6551090</v>
       </c>
       <c r="S383" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -47428,22 +47424,27 @@
       </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>Spelflygande enkelbeckasin</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -47458,49 +47459,49 @@
       <c r="AT383" t="inlineStr"/>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954456</t>
+          <t>https://artportalen.se/Sighting/124287073</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>104588893</v>
+        <v>104588894</v>
       </c>
       <c r="B384" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
@@ -47582,54 +47583,54 @@
       <c r="AY384" t="inlineStr"/>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104588893</t>
+          <t>https://artportalen.se/Sighting/104588894</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>129339959</v>
+        <v>117954456</v>
       </c>
       <c r="B385" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
       <c r="P385" t="inlineStr">
         <is>
-          <t>Haninge, Haninge, Srm</t>
+          <t>V Simonslund, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>695987</v>
+        <v>695832</v>
       </c>
       <c r="R385" t="n">
-        <v>6551433</v>
+        <v>6551662</v>
       </c>
       <c r="S385" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -47653,22 +47654,22 @@
       </c>
       <c r="Y385" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -47679,36 +47680,31 @@
       </c>
       <c r="AG385" t="b">
         <v>0</v>
-      </c>
-      <c r="AH385" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT385" t="inlineStr"/>
       <c r="AW385" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
       <c r="AZ385" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129339959</t>
+          <t>https://artportalen.se/Sighting/117954456</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>133222014</v>
+        <v>104588893</v>
       </c>
       <c r="B386" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -47733,29 +47729,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I386" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I386" t="inlineStr"/>
+      <c r="K386" t="inlineStr"/>
       <c r="P386" t="inlineStr">
         <is>
-          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
+          <t>O om Lervassaträsk, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>695444</v>
+        <v>696042</v>
       </c>
       <c r="R386" t="n">
-        <v>6551343</v>
+        <v>6551462</v>
       </c>
       <c r="S386" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -47779,22 +47767,22 @@
       </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -47809,73 +47797,65 @@
       <c r="AT386" t="inlineStr"/>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>Sören Lindén</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>Sören Lindén</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133222014</t>
+          <t>https://artportalen.se/Sighting/104588893</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>136778970</v>
+        <v>129339959</v>
       </c>
       <c r="B387" t="n">
-        <v>58164</v>
+        <v>58114</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
-      <c r="L387" t="inlineStr"/>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N387" t="inlineStr"/>
       <c r="P387" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Haninge, Haninge, Srm</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>695903</v>
+        <v>695987</v>
       </c>
       <c r="R387" t="n">
-        <v>6551079</v>
+        <v>6551433</v>
       </c>
       <c r="S387" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -47899,12 +47879,22 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -47915,77 +47905,83 @@
       </c>
       <c r="AG387" t="b">
         <v>0</v>
+      </c>
+      <c r="AH387" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT387" t="inlineStr"/>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778970</t>
+          <t>https://artportalen.se/Sighting/129339959</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>136779009</v>
+        <v>133222014</v>
       </c>
       <c r="B388" t="n">
-        <v>58164</v>
+        <v>58136</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr"/>
-      <c r="K388" t="inlineStr"/>
-      <c r="L388" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N388" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>695797</v>
+        <v>695444</v>
       </c>
       <c r="R388" t="n">
-        <v>6551152</v>
+        <v>6551343</v>
       </c>
       <c r="S388" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -48009,12 +48005,22 @@
       </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -48029,27 +48035,27 @@
       <c r="AT388" t="inlineStr"/>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Sören Lindén</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Sören Lindén</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
       <c r="AZ388" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136779009</t>
+          <t>https://artportalen.se/Sighting/133222014</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>136761848</v>
+        <v>136778970</v>
       </c>
       <c r="B389" t="n">
-        <v>5202</v>
+        <v>58164</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -48057,16 +48063,16 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -48075,19 +48081,27 @@
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
-          <t>Lervassaskogen, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>695491</v>
+        <v>695903</v>
       </c>
       <c r="R389" t="n">
-        <v>6551090</v>
+        <v>6551079</v>
       </c>
       <c r="S389" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -48114,19 +48128,9 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="Z389" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA389" t="inlineStr">
         <is>
           <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -48141,27 +48145,27 @@
       <c r="AT389" t="inlineStr"/>
       <c r="AW389" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
       <c r="AZ389" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136761848</t>
+          <t>https://artportalen.se/Sighting/136778970</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>117954429</v>
+        <v>136779009</v>
       </c>
       <c r="B390" t="n">
-        <v>8455</v>
+        <v>58164</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -48169,39 +48173,42 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
       <c r="M390" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
-          <t>V Simonslund, Ornö, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>695717</v>
+        <v>695797</v>
       </c>
       <c r="R390" t="n">
-        <v>6551081</v>
+        <v>6551152</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -48228,22 +48235,12 @@
       </c>
       <c r="Y390" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="Z390" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="AB390" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -48254,51 +48251,31 @@
       </c>
       <c r="AG390" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ390" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK390" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL390" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO390" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga</t>
-        </is>
       </c>
       <c r="AT390" t="inlineStr"/>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954429</t>
+          <t>https://artportalen.se/Sighting/136779009</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>117954459</v>
+        <v>136761848</v>
       </c>
       <c r="B391" t="n">
-        <v>8455</v>
+        <v>5202</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -48306,42 +48283,37 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I391" t="inlineStr"/>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P391" t="inlineStr">
         <is>
-          <t>V Simonslund, Ornö, Srm</t>
+          <t>Lervassaskogen, Srm</t>
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>696081</v>
+        <v>695491</v>
       </c>
       <c r="R391" t="n">
-        <v>6551737</v>
+        <v>6551090</v>
       </c>
       <c r="S391" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T391" t="inlineStr">
         <is>
@@ -48365,22 +48337,22 @@
       </c>
       <c r="Y391" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z391" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD391" t="b">
@@ -48391,51 +48363,31 @@
       </c>
       <c r="AG391" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ391" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK391" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL391" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO391" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga</t>
-        </is>
       </c>
       <c r="AT391" t="inlineStr"/>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
       <c r="AZ391" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954459</t>
+          <t>https://artportalen.se/Sighting/136761848</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>136761835</v>
+        <v>117954429</v>
       </c>
       <c r="B392" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -48461,19 +48413,24 @@
         </is>
       </c>
       <c r="I392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P392" t="inlineStr">
         <is>
-          <t>Lervassaskogen, Srm</t>
+          <t>V Simonslund, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>695422</v>
+        <v>695717</v>
       </c>
       <c r="R392" t="n">
-        <v>6551184</v>
+        <v>6551081</v>
       </c>
       <c r="S392" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>
@@ -48497,22 +48454,22 @@
       </c>
       <c r="Y392" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z392" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD392" t="b">
@@ -48523,31 +48480,51 @@
       </c>
       <c r="AG392" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ392" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK392" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL392" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AO392" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga</t>
+        </is>
       </c>
       <c r="AT392" t="inlineStr"/>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136761835</t>
+          <t>https://artportalen.se/Sighting/117954429</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>117954455</v>
+        <v>117954459</v>
       </c>
       <c r="B393" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -48555,21 +48532,21 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I393" t="inlineStr"/>
@@ -48584,10 +48561,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>695825</v>
+        <v>696081</v>
       </c>
       <c r="R393" t="n">
-        <v>6551645</v>
+        <v>6551737</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -48619,7 +48596,7 @@
       </c>
       <c r="Z393" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
@@ -48629,7 +48606,7 @@
       </c>
       <c r="AB393" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD393" t="b">
@@ -48643,22 +48620,22 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL393" t="inlineStr">
         <is>
-          <t>Björklåga</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AO393" t="inlineStr">
         <is>
-          <t>Betula # Björklåga</t>
+          <t>Pinus sylvestris # Tallåga</t>
         </is>
       </c>
       <c r="AT393" t="inlineStr"/>
@@ -48675,16 +48652,16 @@
       <c r="AY393" t="inlineStr"/>
       <c r="AZ393" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954455</t>
+          <t>https://artportalen.se/Sighting/117954459</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>133164423</v>
+        <v>136761835</v>
       </c>
       <c r="B394" t="n">
-        <v>56896</v>
+        <v>8463</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -48692,41 +48669,37 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>208257</v>
+        <v>106545</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr"/>
       <c r="P394" t="inlineStr">
         <is>
-          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
+          <t>Lervassaskogen, Srm</t>
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>695580</v>
+        <v>695422</v>
       </c>
       <c r="R394" t="n">
-        <v>6550925</v>
+        <v>6551184</v>
       </c>
       <c r="S394" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -48750,22 +48723,22 @@
       </c>
       <c r="Y394" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z394" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB394" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD394" t="b">
@@ -48780,27 +48753,27 @@
       <c r="AT394" t="inlineStr"/>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>Sören Lindén</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>Sören Lindén</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133164423</t>
+          <t>https://artportalen.se/Sighting/136761835</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>128994491</v>
+        <v>117954455</v>
       </c>
       <c r="B395" t="n">
-        <v>56905</v>
+        <v>8444</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -48808,46 +48781,42 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>208260</v>
+        <v>106554</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I395" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P395" t="inlineStr">
         <is>
-          <t>Haninge, Haninge, Srm</t>
+          <t>V Simonslund, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>695917</v>
+        <v>695825</v>
       </c>
       <c r="R395" t="n">
-        <v>6551239</v>
+        <v>6551645</v>
       </c>
       <c r="S395" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -48871,22 +48840,22 @@
       </c>
       <c r="Y395" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z395" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA395" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB395" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD395" t="b">
@@ -48898,35 +48867,50 @@
       <c r="AG395" t="b">
         <v>0</v>
       </c>
-      <c r="AH395" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
+      <c r="AJ395" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK395" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL395" t="inlineStr">
+        <is>
+          <t>Björklåga</t>
+        </is>
+      </c>
+      <c r="AO395" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga</t>
         </is>
       </c>
       <c r="AT395" t="inlineStr"/>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
       <c r="AZ395" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128994491</t>
+          <t>https://artportalen.se/Sighting/117954455</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>126198336</v>
+        <v>133164423</v>
       </c>
       <c r="B396" t="n">
-        <v>99035</v>
+        <v>56896</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -48934,21 +48918,21 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>219790</v>
+        <v>208257</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -48956,26 +48940,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K396" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P396" t="inlineStr">
         <is>
           <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>695946</v>
+        <v>695580</v>
       </c>
       <c r="R396" t="n">
-        <v>6551080</v>
+        <v>6550925</v>
       </c>
       <c r="S396" t="n">
         <v>2</v>
@@ -49002,22 +48976,22 @@
       </c>
       <c r="Y396" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z396" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD396" t="b">
@@ -49028,36 +49002,31 @@
       </c>
       <c r="AG396" t="b">
         <v>0</v>
-      </c>
-      <c r="AH396" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT396" t="inlineStr"/>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Sören Lindén</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Sören Lindén</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
       <c r="AZ396" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126198336</t>
+          <t>https://artportalen.se/Sighting/133164423</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>136743158</v>
+        <v>128994491</v>
       </c>
       <c r="B397" t="n">
-        <v>111330</v>
+        <v>56905</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -49065,37 +49034,46 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>220240</v>
+        <v>208260</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I397" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P397" t="inlineStr">
         <is>
-          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
+          <t>Haninge, Haninge, Srm</t>
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>695941</v>
+        <v>695917</v>
       </c>
       <c r="R397" t="n">
-        <v>6551100</v>
+        <v>6551239</v>
       </c>
       <c r="S397" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T397" t="inlineStr">
         <is>
@@ -49119,12 +49097,22 @@
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -49135,31 +49123,36 @@
       </c>
       <c r="AG397" t="b">
         <v>0</v>
+      </c>
+      <c r="AH397" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT397" t="inlineStr"/>
       <c r="AW397" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
       <c r="AZ397" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136743158</t>
+          <t>https://artportalen.se/Sighting/128994491</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>136750594</v>
+        <v>126198336</v>
       </c>
       <c r="B398" t="n">
-        <v>111330</v>
+        <v>99035</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -49167,37 +49160,51 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I398" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P398" t="inlineStr">
         <is>
           <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>695632</v>
+        <v>695946</v>
       </c>
       <c r="R398" t="n">
-        <v>6550915</v>
+        <v>6551080</v>
       </c>
       <c r="S398" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T398" t="inlineStr">
         <is>
@@ -49221,12 +49228,22 @@
       </c>
       <c r="Y398" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB398" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD398" t="b">
@@ -49237,28 +49254,33 @@
       </c>
       <c r="AG398" t="b">
         <v>0</v>
+      </c>
+      <c r="AH398" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT398" t="inlineStr"/>
       <c r="AW398" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
       <c r="AZ398" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136750594</t>
+          <t>https://artportalen.se/Sighting/126198336</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>136778962</v>
+        <v>136743158</v>
       </c>
       <c r="B399" t="n">
         <v>111330</v>
@@ -49287,20 +49309,16 @@
         </is>
       </c>
       <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr"/>
-      <c r="N399" t="inlineStr"/>
       <c r="P399" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>695953</v>
+        <v>695941</v>
       </c>
       <c r="R399" t="n">
-        <v>6551118</v>
+        <v>6551100</v>
       </c>
       <c r="S399" t="n">
         <v>10</v>
@@ -49341,34 +49359,33 @@
       <c r="AE399" t="b">
         <v>0</v>
       </c>
-      <c r="AF399" t="inlineStr"/>
       <c r="AG399" t="b">
         <v>0</v>
       </c>
       <c r="AT399" t="inlineStr"/>
       <c r="AW399" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
       <c r="AZ399" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778962</t>
+          <t>https://artportalen.se/Sighting/136743158</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>104589382</v>
+        <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>106244</v>
+        <v>111330</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49376,38 +49393,37 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>221144</v>
+        <v>220240</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>695770</v>
+        <v>695632</v>
       </c>
       <c r="R400" t="n">
-        <v>6551567</v>
+        <v>6550915</v>
       </c>
       <c r="S400" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T400" t="inlineStr">
         <is>
@@ -49431,22 +49447,12 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z400" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB400" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD400" t="b">
@@ -49461,27 +49467,27 @@
       <c r="AT400" t="inlineStr"/>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
       <c r="AZ400" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104589382</t>
+          <t>https://artportalen.se/Sighting/136750594</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>104593080</v>
+        <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>106244</v>
+        <v>111330</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -49489,38 +49495,41 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>221144</v>
+        <v>220240</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>695935</v>
+        <v>695953</v>
       </c>
       <c r="R401" t="n">
-        <v>6551092</v>
+        <v>6551118</v>
       </c>
       <c r="S401" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -49544,22 +49553,12 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z401" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB401" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD401" t="b">
@@ -49568,30 +49567,31 @@
       <c r="AE401" t="b">
         <v>0</v>
       </c>
+      <c r="AF401" t="inlineStr"/>
       <c r="AG401" t="b">
         <v>0</v>
       </c>
       <c r="AT401" t="inlineStr"/>
       <c r="AW401" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
       <c r="AZ401" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104593080</t>
+          <t>https://artportalen.se/Sighting/136778962</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>104593123</v>
+        <v>104589382</v>
       </c>
       <c r="B402" t="n">
         <v>106244</v>
@@ -49623,17 +49623,17 @@
       <c r="K402" t="inlineStr"/>
       <c r="P402" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>696047</v>
+        <v>695770</v>
       </c>
       <c r="R402" t="n">
-        <v>6551249</v>
+        <v>6551567</v>
       </c>
       <c r="S402" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
       </c>
       <c r="Z402" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA402" t="inlineStr">
@@ -49672,7 +49672,7 @@
       </c>
       <c r="AB402" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD402" t="b">
@@ -49687,24 +49687,24 @@
       <c r="AT402" t="inlineStr"/>
       <c r="AW402" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
       <c r="AZ402" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104593123</t>
+          <t>https://artportalen.se/Sighting/104589382</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>123451129</v>
+        <v>104593080</v>
       </c>
       <c r="B403" t="n">
         <v>106244</v>
@@ -49732,29 +49732,21 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
       <c r="P403" t="inlineStr">
         <is>
-          <t>Haninge, Haninge, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>695946</v>
+        <v>695935</v>
       </c>
       <c r="R403" t="n">
-        <v>6551298</v>
+        <v>6551092</v>
       </c>
       <c r="S403" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -49778,22 +49770,22 @@
       </c>
       <c r="Y403" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="Z403" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AB403" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD403" t="b">
@@ -49804,36 +49796,31 @@
       </c>
       <c r="AG403" t="b">
         <v>0</v>
-      </c>
-      <c r="AH403" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT403" t="inlineStr"/>
       <c r="AW403" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
       <c r="AZ403" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123451129</t>
+          <t>https://artportalen.se/Sighting/104593080</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>136779069</v>
+        <v>104593123</v>
       </c>
       <c r="B404" t="n">
-        <v>106492</v>
+        <v>106244</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -49859,23 +49846,20 @@
         </is>
       </c>
       <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
-      <c r="L404" t="inlineStr"/>
-      <c r="N404" t="inlineStr"/>
       <c r="P404" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>695554</v>
+        <v>696047</v>
       </c>
       <c r="R404" t="n">
-        <v>6551003</v>
+        <v>6551249</v>
       </c>
       <c r="S404" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -49899,12 +49883,22 @@
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="AB404" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD404" t="b">
@@ -49913,34 +49907,33 @@
       <c r="AE404" t="b">
         <v>0</v>
       </c>
-      <c r="AF404" t="inlineStr"/>
       <c r="AG404" t="b">
         <v>0</v>
       </c>
       <c r="AT404" t="inlineStr"/>
       <c r="AW404" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
       <c r="AZ404" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136779069</t>
+          <t>https://artportalen.se/Sighting/104593123</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>117954427</v>
+        <v>123451129</v>
       </c>
       <c r="B405" t="n">
-        <v>97983</v>
+        <v>106244</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -49948,37 +49941,46 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I405" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P405" t="inlineStr">
         <is>
-          <t>V Simonslund, Ornö, Srm</t>
+          <t>Haninge, Haninge, Srm</t>
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>695713</v>
+        <v>695946</v>
       </c>
       <c r="R405" t="n">
-        <v>6550921</v>
+        <v>6551298</v>
       </c>
       <c r="S405" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -50002,22 +50004,22 @@
       </c>
       <c r="Y405" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="Z405" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA405" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AB405" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD405" t="b">
@@ -50028,31 +50030,36 @@
       </c>
       <c r="AG405" t="b">
         <v>0</v>
+      </c>
+      <c r="AH405" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT405" t="inlineStr"/>
       <c r="AW405" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
       <c r="AZ405" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954427</t>
+          <t>https://artportalen.se/Sighting/123451129</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>117954457</v>
+        <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>97983</v>
+        <v>106492</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -50060,34 +50067,38 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
       <c r="P406" t="inlineStr">
         <is>
-          <t>V Simonslund, Ornö, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>695895</v>
+        <v>695554</v>
       </c>
       <c r="R406" t="n">
-        <v>6551689</v>
+        <v>6551003</v>
       </c>
       <c r="S406" t="n">
         <v>10</v>
@@ -50114,22 +50125,12 @@
       </c>
       <c r="Y406" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="Z406" t="inlineStr">
-        <is>
-          <t>10:35</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA406" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="AB406" t="inlineStr">
-        <is>
-          <t>10:35</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD406" t="b">
@@ -50138,73 +50139,72 @@
       <c r="AE406" t="b">
         <v>0</v>
       </c>
+      <c r="AF406" t="inlineStr"/>
       <c r="AG406" t="b">
         <v>0</v>
       </c>
       <c r="AT406" t="inlineStr"/>
       <c r="AW406" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117954457</t>
+          <t>https://artportalen.se/Sighting/136779069</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>129106452</v>
+        <v>117954427</v>
       </c>
       <c r="B407" t="n">
-        <v>93218</v>
+        <v>97983</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>6331648</v>
+        <v>221945</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr"/>
-      <c r="N407" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr"/>
       <c r="P407" t="inlineStr">
         <is>
-          <t>Bergbrottet, Srm</t>
+          <t>V Simonslund, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>696073</v>
+        <v>695713</v>
       </c>
       <c r="R407" t="n">
-        <v>6551340</v>
+        <v>6550921</v>
       </c>
       <c r="S407" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -50228,22 +50228,22 @@
       </c>
       <c r="Y407" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z407" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA407" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB407" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD407" t="b">
@@ -50252,23 +50252,249 @@
       <c r="AE407" t="b">
         <v>0</v>
       </c>
-      <c r="AF407" t="inlineStr"/>
       <c r="AG407" t="b">
         <v>0</v>
       </c>
       <c r="AT407" t="inlineStr"/>
       <c r="AW407" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX407" t="inlineStr">
         <is>
-          <t>Emilia Blixt, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
       <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954427</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>117954457</v>
+      </c>
+      <c r="B408" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr"/>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>V Simonslund, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>695895</v>
+      </c>
+      <c r="R408" t="n">
+        <v>6551689</v>
+      </c>
+      <c r="S408" t="n">
+        <v>10</v>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD408" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE408" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG408" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT408" t="inlineStr"/>
+      <c r="AW408" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX408" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954457</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>129106452</v>
+      </c>
+      <c r="B409" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>Bergbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>696073</v>
+      </c>
+      <c r="R409" t="n">
+        <v>6551340</v>
+      </c>
+      <c r="S409" t="n">
+        <v>6</v>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD409" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE409" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF409" t="inlineStr"/>
+      <c r="AG409" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT409" t="inlineStr"/>
+      <c r="AW409" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX409" t="inlineStr">
+        <is>
+          <t>Emilia Blixt, Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129106452</t>
         </is>
@@ -50682,6 +50908,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96578</v>
+        <v>96580</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96580</v>
+        <v>96586</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>136779157</v>
       </c>
       <c r="B372" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>136778970</v>
       </c>
       <c r="B389" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>136779009</v>
       </c>
       <c r="B390" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>136779157</v>
       </c>
       <c r="B372" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>136778970</v>
       </c>
       <c r="B389" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>136779009</v>
       </c>
       <c r="B390" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>136761835</v>
       </c>
       <c r="B394" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -46126,16 +46126,8 @@
         </is>
       </c>
       <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
       <c r="N372" t="inlineStr"/>
       <c r="P372" t="inlineStr">
         <is>
@@ -47281,11 +47273,7 @@
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M382" t="inlineStr"/>
       <c r="P382" t="inlineStr">
         <is>
           <t>Lilla Ladängen, Lilla Ladängen, Srm</t>
@@ -48083,11 +48071,7 @@
       <c r="I389" t="inlineStr"/>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
@@ -48193,11 +48177,7 @@
       <c r="I390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>136779157</v>
       </c>
       <c r="B372" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>136761840</v>
       </c>
       <c r="B373" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>136761839</v>
       </c>
       <c r="B377" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -46773,7 +46773,7 @@
         <v>136763388</v>
       </c>
       <c r="B378" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>136763392</v>
       </c>
       <c r="B380" t="n">
-        <v>5181</v>
+        <v>5187</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>136747650</v>
       </c>
       <c r="B382" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>136778970</v>
       </c>
       <c r="B389" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>136779009</v>
       </c>
       <c r="B390" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>136761848</v>
       </c>
       <c r="B391" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>136761835</v>
       </c>
       <c r="B394" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>136743600</v>
       </c>
       <c r="B13" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136750513</v>
       </c>
       <c r="B14" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136746702</v>
       </c>
       <c r="B57" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>136746746</v>
       </c>
       <c r="B156" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136751522</v>
       </c>
       <c r="B157" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>136746871</v>
       </c>
       <c r="B171" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>136743158</v>
       </c>
       <c r="B399" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>136750594</v>
       </c>
       <c r="B400" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>136761827</v>
       </c>
       <c r="B306" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>136761831</v>
       </c>
       <c r="B307" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>136761834</v>
       </c>
       <c r="B308" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>136761846</v>
       </c>
       <c r="B309" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>136779157</v>
       </c>
       <c r="B372" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>136778970</v>
       </c>
       <c r="B389" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>136779009</v>
       </c>
       <c r="B390" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>

--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -6771,7 +6771,7 @@
         <v>136761823</v>
       </c>
       <c r="B53" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136761829</v>
       </c>
       <c r="B54" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>136761842</v>
       </c>
       <c r="B55" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136761849</v>
       </c>
       <c r="B56" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>136761844</v>
       </c>
       <c r="B128" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>136763384</v>
       </c>
       <c r="B159" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>136763386</v>
       </c>
       <c r="B160" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>136779182</v>
       </c>
       <c r="B161" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>136763382</v>
       </c>
       <c r="B287" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>136778962</v>
       </c>
       <c r="B401" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>136779069</v>
       </c>
       <c r="B406" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
